--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$122</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4885" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,7 +666,7 @@
 </t>
   </si>
   <si>
-    <t>Fixed to the generic Visual acuity concept; specific detail lives in the discrete components below, not in code</t>
+    <t>LOINC 98497-1 — Visual acuity panel; specific detail lives in the discrete components below</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -676,6 +676,15 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="98497-1"/&gt;
+    &lt;display value="Visual acuity panel"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>example</t>
@@ -1732,22 +1741,16 @@
     <t>Observation.component:chart.code</t>
   </si>
   <si>
-    <t>The chart or optotype used (e.g. Snellen, ETDRS, LogMAR chart)</t>
-  </si>
-  <si>
-    <t>Observation.component:chart.code.id</t>
-  </si>
-  <si>
-    <t>Observation.component:chart.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:chart.code.coding</t>
-  </si>
-  <si>
-    <t>Observation.component:chart.code.text</t>
-  </si>
-  <si>
-    <t>Chart</t>
+    <t>LOINC 79908-0 — chart or optotype used (Snellen, ETDRS, LogMAR chart)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="79908-0"/&gt;
+    &lt;display value="Type of Visual acuity exam method"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:chart.value[x]</t>
@@ -2184,7 +2187,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP126"/>
+  <dimension ref="A1:AP122"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.6640625" customWidth="true" bestFit="true"/>
@@ -4092,7 +4095,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4107,13 +4110,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4146,30 +4149,30 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4192,19 +4195,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4253,7 +4256,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4268,19 +4271,19 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -4288,10 +4291,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4314,16 +4317,16 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4373,7 +4376,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4394,13 +4397,13 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4408,14 +4411,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4434,19 +4437,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4495,7 +4498,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4510,19 +4513,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4530,14 +4533,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4556,19 +4559,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4617,7 +4620,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4632,19 +4635,19 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4652,10 +4655,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4678,16 +4681,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4737,7 +4740,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4758,13 +4761,13 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4772,10 +4775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4798,17 +4801,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4857,7 +4860,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4872,19 +4875,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4892,10 +4895,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4918,19 +4921,19 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4967,17 +4970,17 @@
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4986,7 +4989,7 @@
         <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
@@ -4995,30 +4998,30 @@
         <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>83</v>
@@ -5043,16 +5046,16 @@
         <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5081,7 +5084,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5099,7 +5102,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5108,7 +5111,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -5117,27 +5120,27 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5163,16 +5166,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5197,13 +5200,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5221,7 +5224,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5230,7 +5233,7 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -5245,7 +5248,7 @@
         <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5256,14 +5259,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5285,16 +5288,16 @@
         <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5319,13 +5322,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5343,7 +5346,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5361,27 +5364,27 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5404,19 +5407,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5465,7 +5468,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5486,10 +5489,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5500,10 +5503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5529,13 +5532,13 @@
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5561,13 +5564,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5585,7 +5588,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5603,27 +5606,27 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5646,13 +5649,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5703,7 +5706,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5727,7 +5730,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5738,10 +5741,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5770,7 +5773,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5811,19 +5814,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5847,7 +5850,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5858,13 +5861,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>83</v>
@@ -5886,13 +5889,13 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5943,7 +5946,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5978,10 +5981,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6004,13 +6007,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6061,7 +6064,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6085,7 +6088,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6096,10 +6099,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6125,10 +6128,10 @@
         <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6167,19 +6170,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6214,10 +6217,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6243,13 +6246,13 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6257,7 +6260,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6299,7 +6302,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>94</v>
@@ -6334,10 +6337,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6360,13 +6363,13 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6417,7 +6420,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6452,10 +6455,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6478,19 +6481,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6539,7 +6542,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6560,10 +6563,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6574,10 +6577,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6600,19 +6603,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6661,7 +6664,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6682,10 +6685,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6696,10 +6699,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6725,16 +6728,16 @@
         <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6759,13 +6762,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6783,7 +6786,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6804,10 +6807,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6818,10 +6821,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6844,16 +6847,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6903,7 +6906,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6921,27 +6924,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6964,16 +6967,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7023,7 +7026,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7041,27 +7044,27 @@
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7084,19 +7087,19 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7145,7 +7148,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7157,7 +7160,7 @@
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -7166,10 +7169,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7180,10 +7183,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7206,13 +7209,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7263,7 +7266,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7287,7 +7290,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7298,10 +7301,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7330,7 +7333,7 @@
         <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>143</v>
@@ -7383,7 +7386,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7407,7 +7410,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7418,14 +7421,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7447,10 +7450,10 @@
         <v>140</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>143</v>
@@ -7505,7 +7508,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7540,10 +7543,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7566,13 +7569,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7623,7 +7626,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7632,7 +7635,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7644,10 +7647,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7658,10 +7661,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7684,13 +7687,13 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7741,7 +7744,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7750,7 +7753,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7762,10 +7765,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7776,10 +7779,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7805,16 +7808,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7842,10 +7845,10 @@
         <v>118</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7863,7 +7866,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7881,13 +7884,13 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7898,10 +7901,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7927,16 +7930,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7961,13 +7964,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7985,7 +7988,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8003,13 +8006,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8020,10 +8023,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8046,17 +8049,17 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8105,7 +8108,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8129,7 +8132,7 @@
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8140,10 +8143,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8166,13 +8169,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8223,7 +8226,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8244,10 +8247,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8258,10 +8261,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8284,16 +8287,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8343,7 +8346,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8364,10 +8367,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8378,10 +8381,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8404,16 +8407,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8463,7 +8466,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8484,10 +8487,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8498,10 +8501,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8524,19 +8527,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8573,17 +8576,17 @@
         <v>83</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8604,10 +8607,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8618,10 +8621,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8644,13 +8647,13 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8701,7 +8704,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8725,7 +8728,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8736,10 +8739,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8768,7 +8771,7 @@
         <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -8821,7 +8824,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8845,7 +8848,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8856,14 +8859,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8885,10 +8888,10 @@
         <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -8943,7 +8946,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8978,10 +8981,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9007,13 +9010,13 @@
         <v>192</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>207</v>
@@ -9041,13 +9044,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -9065,7 +9068,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>94</v>
@@ -9083,16 +9086,16 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9100,10 +9103,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9126,19 +9129,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9187,7 +9190,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9205,27 +9208,27 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9251,16 +9254,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9285,13 +9288,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9309,7 +9312,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9318,7 +9321,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9333,7 +9336,7 @@
         <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9344,14 +9347,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9373,16 +9376,16 @@
         <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9407,13 +9410,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9431,7 +9434,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9449,27 +9452,27 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9495,16 +9498,16 @@
         <v>84</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9553,7 +9556,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9574,10 +9577,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9588,13 +9591,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>83</v>
@@ -9616,19 +9619,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9677,7 +9680,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9698,10 +9701,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9712,10 +9715,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9738,13 +9741,13 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9795,7 +9798,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9819,7 +9822,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9830,10 +9833,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9862,7 +9865,7 @@
         <v>141</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>143</v>
@@ -9915,7 +9918,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9939,7 +9942,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9950,14 +9953,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9979,10 +9982,10 @@
         <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>143</v>
@@ -10037,7 +10040,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10072,10 +10075,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10101,13 +10104,13 @@
         <v>192</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>207</v>
@@ -10135,13 +10138,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10159,7 +10162,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>94</v>
@@ -10177,16 +10180,16 @@
         <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10194,10 +10197,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10220,13 +10223,13 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10277,7 +10280,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10301,7 +10304,7 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10312,10 +10315,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10344,7 +10347,7 @@
         <v>141</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -10385,19 +10388,19 @@
         <v>83</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10421,7 +10424,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10432,10 +10435,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10458,19 +10461,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10519,7 +10522,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10540,10 +10543,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10554,10 +10557,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10580,19 +10583,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10602,7 +10605,7 @@
         <v>83</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>83</v>
@@ -10641,7 +10644,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10662,10 +10665,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10676,10 +10679,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10702,19 +10705,19 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10763,7 +10766,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10781,27 +10784,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10827,16 +10830,16 @@
         <v>192</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10861,13 +10864,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10885,7 +10888,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10894,7 +10897,7 @@
         <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>106</v>
@@ -10909,7 +10912,7 @@
         <v>137</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10920,14 +10923,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10949,16 +10952,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10983,13 +10986,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -11007,7 +11010,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11025,27 +11028,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11071,16 +11074,16 @@
         <v>84</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11129,7 +11132,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11150,10 +11153,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11164,13 +11167,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>83</v>
@@ -11192,19 +11195,19 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11253,7 +11256,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11274,10 +11277,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11288,10 +11291,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11314,13 +11317,13 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11371,7 +11374,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11395,7 +11398,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11406,10 +11409,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11438,7 +11441,7 @@
         <v>141</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11491,7 +11494,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11515,7 +11518,7 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11526,14 +11529,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11555,10 +11558,10 @@
         <v>140</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>143</v>
@@ -11613,7 +11616,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11648,10 +11651,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11677,13 +11680,13 @@
         <v>192</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>207</v>
@@ -11711,13 +11714,13 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11735,7 +11738,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>94</v>
@@ -11753,16 +11756,16 @@
         <v>83</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -11770,10 +11773,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11796,13 +11799,13 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11853,7 +11856,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11877,7 +11880,7 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11888,10 +11891,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11920,7 +11923,7 @@
         <v>141</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11961,19 +11964,19 @@
         <v>83</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11997,7 +12000,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12008,10 +12011,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12034,19 +12037,19 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12095,7 +12098,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12116,10 +12119,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12130,10 +12133,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12156,19 +12159,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12178,7 +12181,7 @@
         <v>83</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>83</v>
@@ -12217,7 +12220,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12238,10 +12241,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12252,10 +12255,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12281,16 +12284,16 @@
         <v>192</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12339,7 +12342,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12357,27 +12360,27 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12403,16 +12406,16 @@
         <v>192</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12437,13 +12440,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12461,7 +12464,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12470,7 +12473,7 @@
         <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>106</v>
@@ -12485,7 +12488,7 @@
         <v>137</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12496,14 +12499,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12525,16 +12528,16 @@
         <v>192</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12559,13 +12562,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12583,7 +12586,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12601,27 +12604,27 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12647,16 +12650,16 @@
         <v>84</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12705,7 +12708,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12726,10 +12729,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12740,13 +12743,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>83</v>
@@ -12768,19 +12771,19 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12829,7 +12832,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12850,10 +12853,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12864,10 +12867,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12890,13 +12893,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12947,7 +12950,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12971,7 +12974,7 @@
         <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12982,10 +12985,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13014,7 +13017,7 @@
         <v>141</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>143</v>
@@ -13067,7 +13070,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13091,7 +13094,7 @@
         <v>83</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13102,14 +13105,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13131,10 +13134,10 @@
         <v>140</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>143</v>
@@ -13189,7 +13192,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13224,10 +13227,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13253,13 +13256,13 @@
         <v>192</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>207</v>
@@ -13272,7 +13275,7 @@
         <v>83</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>83</v>
@@ -13287,13 +13290,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13311,7 +13314,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>94</v>
@@ -13329,16 +13332,16 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -13346,10 +13349,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13369,19 +13372,23 @@
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>329</v>
+        <v>192</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>330</v>
+        <v>492</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13429,7 +13436,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>332</v>
+        <v>490</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13441,44 +13448,44 @@
         <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13490,18 +13497,20 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>141</v>
+        <v>496</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>335</v>
+        <v>497</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13525,43 +13534,43 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>338</v>
+        <v>495</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>83</v>
@@ -13570,10 +13579,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13584,14 +13593,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13607,22 +13616,22 @@
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>364</v>
+        <v>192</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>366</v>
+        <v>302</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13647,13 +13656,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13671,7 +13680,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>369</v>
+        <v>499</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13689,27 +13698,27 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13720,7 +13729,7 @@
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -13729,22 +13738,22 @@
         <v>83</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>373</v>
+        <v>501</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>374</v>
+        <v>502</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13754,7 +13763,7 @@
         <v>83</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>550</v>
+        <v>83</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>83</v>
@@ -13793,13 +13802,13 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>377</v>
+        <v>500</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>83</v>
@@ -13814,10 +13823,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13826,14 +13835,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13845,7 +13856,7 @@
         <v>94</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>83</v>
@@ -13854,19 +13865,19 @@
         <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>192</v>
+        <v>409</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>275</v>
+        <v>476</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>277</v>
+        <v>478</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13915,13 +13926,13 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>83</v>
@@ -13933,27 +13944,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>493</v>
+        <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>282</v>
+        <v>480</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>283</v>
+        <v>481</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>284</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13976,20 +13987,16 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>495</v>
+        <v>331</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -14013,13 +14020,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -14037,7 +14044,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>494</v>
+        <v>333</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14046,10 +14053,10 @@
         <v>94</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
@@ -14058,10 +14065,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14072,14 +14079,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>299</v>
+        <v>139</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14098,20 +14105,18 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>300</v>
+        <v>141</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>83</v>
       </c>
@@ -14135,13 +14140,13 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14159,7 +14164,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>498</v>
+        <v>339</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14171,37 +14176,37 @@
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>306</v>
+        <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>309</v>
+        <v>83</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14214,25 +14219,25 @@
         <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>500</v>
+        <v>421</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>501</v>
+        <v>422</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>411</v>
+        <v>143</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>412</v>
+        <v>149</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14281,7 +14286,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>499</v>
+        <v>423</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14293,7 +14298,7 @@
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>83</v>
@@ -14302,10 +14307,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>415</v>
+        <v>137</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14314,28 +14319,26 @@
         <v>83</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>83</v>
@@ -14344,19 +14347,19 @@
         <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>408</v>
+        <v>192</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>474</v>
+        <v>558</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>477</v>
+        <v>207</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14381,13 +14384,13 @@
         <v>83</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -14405,13 +14408,13 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
@@ -14423,16 +14426,16 @@
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>83</v>
+        <v>489</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>479</v>
+        <v>214</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>480</v>
+        <v>215</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -14440,10 +14443,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>481</v>
+        <v>510</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14466,13 +14469,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14523,7 +14526,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14547,7 +14550,7 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14558,10 +14561,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14590,7 +14593,7 @@
         <v>141</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>143</v>
@@ -14631,19 +14634,19 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14667,7 +14670,7 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14678,14 +14681,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14698,25 +14701,25 @@
         <v>83</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J104" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>420</v>
+        <v>366</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>143</v>
+        <v>368</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>149</v>
+        <v>369</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -14765,7 +14768,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>422</v>
+        <v>370</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14777,7 +14780,7 @@
         <v>83</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>83</v>
@@ -14786,10 +14789,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>137</v>
+        <v>372</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14800,10 +14803,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14811,7 +14814,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>94</v>
@@ -14826,19 +14829,19 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>561</v>
+        <v>374</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>486</v>
+        <v>375</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>487</v>
+        <v>376</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>207</v>
+        <v>377</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -14848,7 +14851,7 @@
         <v>83</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>83</v>
+        <v>563</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>83</v>
@@ -14863,13 +14866,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14887,10 +14890,10 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>484</v>
+        <v>378</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>94</v>
@@ -14905,16 +14908,16 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>213</v>
+        <v>379</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>214</v>
+        <v>380</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
@@ -14922,10 +14925,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14945,19 +14948,23 @@
         <v>83</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>329</v>
+        <v>192</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>330</v>
+        <v>492</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
       </c>
@@ -15005,7 +15012,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>332</v>
+        <v>490</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15017,44 +15024,44 @@
         <v>83</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>83</v>
@@ -15066,18 +15073,20 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>141</v>
+        <v>496</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>335</v>
+        <v>497</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
       </c>
@@ -15101,43 +15110,43 @@
         <v>83</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>338</v>
+        <v>495</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>83</v>
@@ -15146,10 +15155,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15160,14 +15169,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15183,22 +15192,22 @@
         <v>83</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>364</v>
+        <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>366</v>
+        <v>302</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15223,13 +15232,13 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15247,7 +15256,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>369</v>
+        <v>499</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15265,27 +15274,27 @@
         <v>83</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15296,7 +15305,7 @@
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>83</v>
@@ -15305,22 +15314,22 @@
         <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>373</v>
+        <v>501</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>374</v>
+        <v>502</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15330,7 +15339,7 @@
         <v>83</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>566</v>
+        <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>83</v>
@@ -15369,13 +15378,13 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>377</v>
+        <v>500</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>83</v>
@@ -15390,10 +15399,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15402,14 +15411,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C110" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="D110" t="s" s="2">
         <v>83</v>
       </c>
@@ -15421,7 +15432,7 @@
         <v>94</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>83</v>
@@ -15430,19 +15441,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>192</v>
+        <v>409</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>275</v>
+        <v>476</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>277</v>
+        <v>478</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15491,13 +15502,13 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
@@ -15509,27 +15520,27 @@
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>493</v>
+        <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>282</v>
+        <v>480</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>283</v>
+        <v>481</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>284</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15552,20 +15563,16 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>495</v>
+        <v>331</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>83</v>
       </c>
@@ -15589,13 +15596,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15613,7 +15620,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>494</v>
+        <v>333</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15622,10 +15629,10 @@
         <v>94</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
@@ -15634,10 +15641,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15648,14 +15655,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>299</v>
+        <v>139</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15674,20 +15681,18 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>300</v>
+        <v>141</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>83</v>
       </c>
@@ -15711,13 +15716,13 @@
         <v>83</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -15735,7 +15740,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>498</v>
+        <v>339</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15747,37 +15752,37 @@
         <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>306</v>
+        <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>309</v>
+        <v>83</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15790,25 +15795,25 @@
         <v>83</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>500</v>
+        <v>421</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>501</v>
+        <v>422</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>411</v>
+        <v>143</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>412</v>
+        <v>149</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -15857,7 +15862,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>499</v>
+        <v>423</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15869,7 +15874,7 @@
         <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
@@ -15878,10 +15883,10 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>415</v>
+        <v>137</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15890,28 +15895,26 @@
         <v>83</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>83</v>
@@ -15920,19 +15923,19 @@
         <v>95</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>408</v>
+        <v>192</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>474</v>
+        <v>574</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>477</v>
+        <v>207</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15957,13 +15960,13 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -15981,13 +15984,13 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>83</v>
@@ -15999,16 +16002,16 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>83</v>
+        <v>489</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>479</v>
+        <v>214</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>480</v>
+        <v>215</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -16016,10 +16019,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>481</v>
+        <v>510</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16042,13 +16045,13 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16099,7 +16102,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16123,7 +16126,7 @@
         <v>83</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16134,10 +16137,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16166,7 +16169,7 @@
         <v>141</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>143</v>
@@ -16207,19 +16210,19 @@
         <v>83</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16243,7 +16246,7 @@
         <v>83</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16254,14 +16257,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16274,25 +16277,25 @@
         <v>83</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>420</v>
+        <v>366</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>143</v>
+        <v>368</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>149</v>
+        <v>369</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16341,7 +16344,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>422</v>
+        <v>370</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16353,7 +16356,7 @@
         <v>83</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>83</v>
@@ -16362,10 +16365,10 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>137</v>
+        <v>372</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16376,10 +16379,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16387,7 +16390,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>94</v>
@@ -16402,19 +16405,19 @@
         <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>577</v>
+        <v>374</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>486</v>
+        <v>375</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>487</v>
+        <v>376</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>207</v>
+        <v>377</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16424,7 +16427,7 @@
         <v>83</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>83</v>
+        <v>579</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>83</v>
@@ -16439,13 +16442,13 @@
         <v>83</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>83</v>
@@ -16463,10 +16466,10 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>484</v>
+        <v>378</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>94</v>
@@ -16481,16 +16484,16 @@
         <v>83</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>213</v>
+        <v>379</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>214</v>
+        <v>380</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>83</v>
@@ -16498,10 +16501,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16521,19 +16524,23 @@
         <v>83</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>329</v>
+        <v>581</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>330</v>
+        <v>492</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
       </c>
@@ -16581,7 +16588,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>332</v>
+        <v>490</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16593,44 +16600,44 @@
         <v>83</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>83</v>
@@ -16642,18 +16649,20 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>141</v>
+        <v>496</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>335</v>
+        <v>497</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>83</v>
       </c>
@@ -16677,43 +16686,43 @@
         <v>83</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>338</v>
+        <v>495</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>83</v>
@@ -16722,10 +16731,10 @@
         <v>83</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -16736,14 +16745,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -16759,22 +16768,22 @@
         <v>83</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>364</v>
+        <v>192</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>366</v>
+        <v>302</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -16799,13 +16808,13 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
@@ -16823,7 +16832,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>369</v>
+        <v>499</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -16841,27 +16850,27 @@
         <v>83</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16872,7 +16881,7 @@
         <v>81</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>83</v>
@@ -16881,22 +16890,22 @@
         <v>83</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>373</v>
+        <v>501</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>374</v>
+        <v>502</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -16906,7 +16915,7 @@
         <v>83</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>582</v>
+        <v>83</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>83</v>
@@ -16945,13 +16954,13 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>377</v>
+        <v>500</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>83</v>
@@ -16966,508 +16975,20 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP126" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP126">
+  <autoFilter ref="A1:AP122">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17477,7 +16998,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI125">
+  <conditionalFormatting sqref="A2:AI121">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ophthalmic-visual-acuity.xlsx
+++ b/StructureDefinition-ophthalmic-visual-acuity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2190,17 +2190,17 @@
   <dimension ref="A1:AP122"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.40625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2209,28 +2209,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.52734375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.296875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
